--- a/Master/KODE DAN RESTO BOM NEW.xlsx
+++ b/Master/KODE DAN RESTO BOM NEW.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FORMAT DAN TEMPLATE\T013_Vba_Spit_data\DEX\Master\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FORMAT DAN TEMPLATE\T013_Vba_Spit_data\DEX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B8AF4E-46A8-499B-96AF-B210E97A300E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{766EB3D5-FA42-466A-AA65-38662169595B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{2A27DFF0-1BDB-46C7-8D34-C6B2AB0C8283}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{2A27DFF0-1BDB-46C7-8D34-C6B2AB0C8283}"/>
   </bookViews>
   <sheets>
     <sheet name="KODE" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="EXCLUDE" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">EXCLUDE!$A$1:$B$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">RESTO!$A$1:$F$115</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="345">
   <si>
     <t>NO</t>
   </si>
@@ -1057,6 +1058,15 @@
   </si>
   <si>
     <t>1209.1-G.Malang - Soekarno Hatta (MLGSOE)</t>
+  </si>
+  <si>
+    <t>CBIPAS</t>
+  </si>
+  <si>
+    <t>1378.1-G.Bogor - Raya Psr Lama Jonggol (CBIPAS)</t>
+  </si>
+  <si>
+    <t>1378.CBIPAS</t>
   </si>
 </sst>
 </file>
@@ -1114,7 +1124,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1199,12 +1209,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FFEA9999"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -1275,7 +1279,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1346,18 +1350,22 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="14" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{7B1D400C-522A-4D8B-AD46-9D4C289835C7}"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1405,6 +1413,14 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2149,7 +2165,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0933A7F-4C29-4A64-8B36-B4F9E885B333}">
-  <dimension ref="A1:F116"/>
+  <dimension ref="A1:F117"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
@@ -3503,7 +3519,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="19">
-        <f t="shared" ref="A65:A115" si="2">1+A64</f>
+        <f t="shared" ref="A65:A117" si="2">1+A64</f>
         <v>62</v>
       </c>
       <c r="B65" s="20" t="s">
@@ -4575,24 +4591,45 @@
       <c r="A116" s="19">
         <v>88</v>
       </c>
-      <c r="B116" s="26" t="s">
+      <c r="B116" s="27" t="s">
         <v>339</v>
       </c>
-      <c r="C116" s="26" t="s">
+      <c r="C116" s="27" t="s">
         <v>340</v>
       </c>
-      <c r="D116" s="26" t="s">
+      <c r="D116" s="27" t="s">
         <v>341</v>
       </c>
-      <c r="E116" s="27">
+      <c r="E116" s="28">
         <v>46197</v>
       </c>
-      <c r="F116" s="25" t="s">
+      <c r="F116" s="29" t="s">
         <v>234</v>
       </c>
     </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="19">
+        <f t="shared" si="2"/>
+        <v>89</v>
+      </c>
+      <c r="B117" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C117" s="19" t="s">
+        <v>342</v>
+      </c>
+      <c r="D117" s="19" t="s">
+        <v>343</v>
+      </c>
+      <c r="E117" s="26">
+        <v>46265</v>
+      </c>
+      <c r="F117" s="5" t="s">
+        <v>344</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="D83:D116">
+  <conditionalFormatting sqref="D83:D117">
     <cfRule type="duplicateValues" dxfId="1" priority="6"/>
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
@@ -4602,7 +4639,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{620FB88A-C9C3-47FD-BB4D-39DF868892A8}">
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
@@ -4691,7 +4728,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="25" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B11" s="4">
         <v>46218</v>
@@ -4699,7 +4736,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="25" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B12" s="4">
         <v>46218</v>
@@ -4707,7 +4744,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="25" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B13" s="4">
         <v>46218</v>
@@ -4715,7 +4752,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="25" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="B14" s="4">
         <v>46218</v>
@@ -4723,7 +4760,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="25" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="B15" s="4">
         <v>46218</v>
@@ -4731,7 +4768,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="25" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="B16" s="4">
         <v>46218</v>
@@ -4739,7 +4776,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="B17" s="4">
         <v>46218</v>
@@ -4747,7 +4784,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="25" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="B18" s="4">
         <v>46218</v>
@@ -4755,7 +4792,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="25" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="B19" s="4">
         <v>46218</v>
@@ -4763,7 +4800,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="25" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="B20" s="4">
         <v>46218</v>
@@ -4771,97 +4808,9 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="25" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="B21" s="4">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="25" t="s">
-        <v>324</v>
-      </c>
-      <c r="B22" s="4">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="25" t="s">
-        <v>325</v>
-      </c>
-      <c r="B23" s="4">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="25" t="s">
-        <v>326</v>
-      </c>
-      <c r="B24" s="4">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="25" t="s">
-        <v>327</v>
-      </c>
-      <c r="B25" s="4">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="25" t="s">
-        <v>328</v>
-      </c>
-      <c r="B26" s="4">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="25" t="s">
-        <v>329</v>
-      </c>
-      <c r="B27" s="4">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="25" t="s">
-        <v>330</v>
-      </c>
-      <c r="B28" s="4">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="25" t="s">
-        <v>331</v>
-      </c>
-      <c r="B29" s="4">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="25" t="s">
-        <v>332</v>
-      </c>
-      <c r="B30" s="4">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="25" t="s">
-        <v>333</v>
-      </c>
-      <c r="B31" s="4">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="25" t="s">
-        <v>334</v>
-      </c>
-      <c r="B32" s="4">
         <v>46218</v>
       </c>
     </row>

--- a/Master/KODE DAN RESTO BOM NEW.xlsx
+++ b/Master/KODE DAN RESTO BOM NEW.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24701"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FORMAT DAN TEMPLATE\T013_Vba_Spit_data\DEX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\BAGAS\bacoba\001.DEX\Master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{766EB3D5-FA42-466A-AA65-38662169595B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF1833F-3C68-4EDF-AABC-A5D8F71A9A64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{2A27DFF0-1BDB-46C7-8D34-C6B2AB0C8283}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{2A27DFF0-1BDB-46C7-8D34-C6B2AB0C8283}"/>
   </bookViews>
   <sheets>
     <sheet name="KODE" sheetId="1" r:id="rId1"/>
@@ -27,12 +27,21 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="364">
   <si>
     <t>NO</t>
   </si>
@@ -1067,6 +1076,63 @@
   </si>
   <si>
     <t>1378.CBIPAS</t>
+  </si>
+  <si>
+    <t>1051.1-G.Malang - Raya Tlogomas (MLGTLO)</t>
+  </si>
+  <si>
+    <t>MLGTLO</t>
+  </si>
+  <si>
+    <t>MLGJAK</t>
+  </si>
+  <si>
+    <t>1016.1-G.Malang - Jakarta (MLGJAK)</t>
+  </si>
+  <si>
+    <t>1016.MLGJAK</t>
+  </si>
+  <si>
+    <t>1051.MLGTLO</t>
+  </si>
+  <si>
+    <t>MLGRON</t>
+  </si>
+  <si>
+    <t>1036.1-G.Malang - Ronggowarsito (MLGRON)</t>
+  </si>
+  <si>
+    <t>1036.MLGRON</t>
+  </si>
+  <si>
+    <t>JAWA TIMUR 1</t>
+  </si>
+  <si>
+    <t>1032.1-G.Batu - W.R Supratman (BTUSUP)</t>
+  </si>
+  <si>
+    <t>1032.BTUSUP</t>
+  </si>
+  <si>
+    <t>BTUSUP</t>
+  </si>
+  <si>
+    <t>1052.1-G.Malang - Raya Mondoroko (MLGMON)</t>
+  </si>
+  <si>
+    <t>MLGMON</t>
+  </si>
+  <si>
+    <t>1052.MLGMON</t>
+  </si>
+  <si>
+    <t>KPNSUD</t>
+  </si>
+  <si>
+    <t>1314.1-G.Malang - Panglima Sudirman (KPNSUD)</t>
+  </si>
+  <si>
+    <t>1314.KPNSUD</t>
   </si>
 </sst>
 </file>
@@ -1279,7 +1345,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1353,19 +1419,12 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{7B1D400C-522A-4D8B-AD46-9D4C289835C7}"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="5">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1413,14 +1472,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1735,14 +1786,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04EABAD4-117C-4DE8-B838-BB6A4F70CD80}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
         <v>156</v>
       </c>
@@ -1750,7 +1801,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="14">
         <v>550064</v>
       </c>
@@ -1758,7 +1809,7 @@
         <v>550364</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="14">
         <v>550065</v>
       </c>
@@ -1766,7 +1817,7 @@
         <v>550365</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="14">
         <v>550080</v>
       </c>
@@ -1774,7 +1825,7 @@
         <v>550366</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="14">
         <v>550081</v>
       </c>
@@ -1782,7 +1833,7 @@
         <v>550367</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="14">
         <v>550260</v>
       </c>
@@ -1790,7 +1841,7 @@
         <v>550368</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="14">
         <v>550261</v>
       </c>
@@ -1798,7 +1849,7 @@
         <v>550369</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="14">
         <v>550262</v>
       </c>
@@ -1806,7 +1857,7 @@
         <v>550370</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="14">
         <v>550263</v>
       </c>
@@ -1814,7 +1865,7 @@
         <v>550371</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="14">
         <v>550264</v>
       </c>
@@ -1822,7 +1873,7 @@
         <v>550372</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="14">
         <v>550265</v>
       </c>
@@ -1830,7 +1881,7 @@
         <v>550373</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="14">
         <v>550266</v>
       </c>
@@ -1838,7 +1889,7 @@
         <v>550374</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="14">
         <v>550267</v>
       </c>
@@ -1846,7 +1897,7 @@
         <v>550375</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="14">
         <v>550268</v>
       </c>
@@ -1854,7 +1905,7 @@
         <v>550376</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="14">
         <v>550269</v>
       </c>
@@ -1862,7 +1913,7 @@
         <v>550377</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="14">
         <v>550270</v>
       </c>
@@ -1870,7 +1921,7 @@
         <v>550378</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="14">
         <v>550271</v>
       </c>
@@ -1878,7 +1929,7 @@
         <v>550379</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="14">
         <v>550146</v>
       </c>
@@ -1886,7 +1937,7 @@
         <v>550430</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="14">
         <v>550151</v>
       </c>
@@ -1894,7 +1945,7 @@
         <v>550431</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="14">
         <v>550152</v>
       </c>
@@ -1902,7 +1953,7 @@
         <v>550432</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="14">
         <v>550153</v>
       </c>
@@ -1910,7 +1961,7 @@
         <v>550433</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="14">
         <v>550154</v>
       </c>
@@ -1927,15 +1978,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB90F88C-CAFF-4807-B167-4FE3417BBD55}">
   <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" customWidth="1"/>
+    <col min="3" max="3" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
         <v>158</v>
       </c>
@@ -1949,202 +2000,202 @@
         <v>157</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B2" s="4"/>
       <c r="C2" s="23"/>
       <c r="D2" s="23"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B3" s="4"/>
       <c r="C3" s="23"/>
       <c r="D3" s="23"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B4" s="4"/>
       <c r="C4" s="23"/>
       <c r="D4" s="23"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B5" s="4"/>
       <c r="C5" s="23"/>
       <c r="D5" s="23"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B6" s="4"/>
       <c r="C6" s="23"/>
       <c r="D6" s="23"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B7" s="4"/>
       <c r="C7" s="23"/>
       <c r="D7" s="23"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B8" s="4"/>
       <c r="C8" s="23"/>
       <c r="D8" s="23"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B9" s="4"/>
       <c r="C9" s="23"/>
       <c r="D9" s="23"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B10" s="4"/>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B11" s="4"/>
       <c r="C11" s="23"/>
       <c r="D11" s="23"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B12" s="4"/>
       <c r="C12" s="23"/>
       <c r="D12" s="23"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B13" s="4"/>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B14" s="4"/>
       <c r="C14" s="23"/>
       <c r="D14" s="23"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B15" s="4"/>
       <c r="C15" s="23"/>
       <c r="D15" s="23"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B16" s="4"/>
       <c r="C16" s="23"/>
       <c r="D16" s="23"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B17" s="4"/>
       <c r="C17" s="23"/>
       <c r="D17" s="23"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B18" s="4"/>
       <c r="C18" s="23"/>
       <c r="D18" s="23"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B19" s="4"/>
       <c r="C19" s="23"/>
       <c r="D19" s="23"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B20" s="4"/>
       <c r="C20" s="23"/>
       <c r="D20" s="23"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B21" s="4"/>
       <c r="C21" s="23"/>
       <c r="D21" s="23"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B22" s="4"/>
       <c r="C22" s="23"/>
       <c r="D22" s="23"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B23" s="4"/>
       <c r="C23" s="23"/>
       <c r="D23" s="23"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B24" s="4"/>
       <c r="C24" s="23"/>
       <c r="D24" s="23"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B25" s="4"/>
       <c r="C25" s="23"/>
       <c r="D25" s="23"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B26" s="4"/>
       <c r="C26" s="23"/>
       <c r="D26" s="23"/>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B27" s="4"/>
       <c r="C27" s="23"/>
       <c r="D27" s="23"/>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B28" s="4"/>
       <c r="C28" s="23"/>
       <c r="D28" s="23"/>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B29" s="4"/>
       <c r="C29" s="23"/>
       <c r="D29" s="23"/>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B30" s="4"/>
       <c r="C30" s="23"/>
       <c r="D30" s="23"/>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B31" s="4"/>
       <c r="C31" s="23"/>
       <c r="D31" s="23"/>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B32" s="4"/>
       <c r="C32" s="23"/>
       <c r="D32" s="23"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B33" s="4"/>
       <c r="C33" s="23"/>
       <c r="D33" s="23"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B34" s="4"/>
       <c r="C34" s="23"/>
       <c r="D34" s="23"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B35" s="4"/>
       <c r="C35" s="23"/>
       <c r="D35" s="23"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B36" s="4"/>
       <c r="C36" s="23"/>
       <c r="D36" s="23"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B37" s="4"/>
       <c r="C37" s="23"/>
       <c r="D37" s="23"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B38" s="4"/>
       <c r="C38" s="23"/>
       <c r="D38" s="23"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B39" s="4"/>
       <c r="C39" s="23"/>
       <c r="D39" s="23"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B40" s="4"/>
       <c r="C40" s="23"/>
       <c r="D40" s="23"/>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B41" s="4"/>
       <c r="C41" s="23"/>
       <c r="D41" s="23"/>
@@ -2165,17 +2216,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0933A7F-4C29-4A64-8B36-B4F9E885B333}">
-  <dimension ref="A1:F117"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F123"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="41.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2195,7 +2246,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -2215,7 +2266,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <f t="shared" ref="A3:A51" si="0">1+A2</f>
         <v>2</v>
@@ -2236,7 +2287,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2257,7 +2308,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2278,7 +2329,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2299,7 +2350,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2320,7 +2371,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2341,7 +2392,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2362,7 +2413,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2383,7 +2434,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2404,7 +2455,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2425,7 +2476,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2446,7 +2497,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2467,7 +2518,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2488,7 +2539,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2509,7 +2560,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2530,7 +2581,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2551,7 +2602,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2572,7 +2623,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2593,7 +2644,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2614,7 +2665,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2635,7 +2686,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -2656,7 +2707,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -2677,7 +2728,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2698,7 +2749,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -2719,7 +2770,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -2740,7 +2791,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -2761,7 +2812,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -2782,7 +2833,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -2803,7 +2854,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -2824,7 +2875,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -2845,7 +2896,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -2866,7 +2917,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -2887,7 +2938,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -2908,7 +2959,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -2929,7 +2980,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -2950,7 +3001,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -2971,7 +3022,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -2992,7 +3043,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -3013,7 +3064,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -3034,7 +3085,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -3055,7 +3106,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -3076,7 +3127,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -3097,7 +3148,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -3118,7 +3169,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -3139,7 +3190,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -3160,7 +3211,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -3181,7 +3232,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -3202,7 +3253,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -3223,7 +3274,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -3244,7 +3295,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -3264,7 +3315,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -3285,7 +3336,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -3306,7 +3357,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -3327,7 +3378,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -3348,7 +3399,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -3369,7 +3420,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -3390,7 +3441,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -3411,7 +3462,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -3432,7 +3483,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -3453,7 +3504,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -3474,7 +3525,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -3495,7 +3546,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="17">
         <f>1+A61</f>
         <v>61</v>
@@ -3517,9 +3568,9 @@
         <v>1053.BGRPAD</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="19">
-        <f t="shared" ref="A65:A117" si="2">1+A64</f>
+        <f t="shared" ref="A65:A119" si="2">1+A64</f>
         <v>62</v>
       </c>
       <c r="B65" s="20" t="s">
@@ -3539,7 +3590,7 @@
         <v>1074.BGRTAJ</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="19">
         <f t="shared" si="2"/>
         <v>63</v>
@@ -3561,7 +3612,7 @@
         <v>1079.BGRSAP</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="19">
         <f t="shared" si="2"/>
         <v>64</v>
@@ -3583,7 +3634,7 @@
         <v>1100.BGRABD</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="19">
         <f t="shared" si="2"/>
         <v>65</v>
@@ -3605,7 +3656,7 @@
         <v>1112.BGRSHO</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="19">
         <f t="shared" si="2"/>
         <v>66</v>
@@ -3627,7 +3678,7 @@
         <v>1190.BGRBAT</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="19">
         <f t="shared" si="2"/>
         <v>67</v>
@@ -3648,7 +3699,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="19">
         <f t="shared" si="2"/>
         <v>68</v>
@@ -3669,7 +3720,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="19">
         <f t="shared" si="2"/>
         <v>69</v>
@@ -3690,7 +3741,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="19">
         <f t="shared" si="2"/>
         <v>70</v>
@@ -3711,7 +3762,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="19">
         <f t="shared" si="2"/>
         <v>71</v>
@@ -3732,7 +3783,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="19">
         <f t="shared" si="2"/>
         <v>72</v>
@@ -3753,7 +3804,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="19">
         <f t="shared" si="2"/>
         <v>73</v>
@@ -3774,7 +3825,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="19">
         <f t="shared" si="2"/>
         <v>74</v>
@@ -3795,7 +3846,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="19">
         <f t="shared" si="2"/>
         <v>75</v>
@@ -3816,7 +3867,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="19">
         <f t="shared" si="2"/>
         <v>76</v>
@@ -3837,7 +3888,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="19">
         <f t="shared" si="2"/>
         <v>77</v>
@@ -3858,7 +3909,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="19">
         <f t="shared" si="2"/>
         <v>78</v>
@@ -3879,7 +3930,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="19">
         <v>79</v>
       </c>
@@ -3899,7 +3950,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" s="19">
         <f t="shared" si="2"/>
         <v>80</v>
@@ -3920,7 +3971,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" s="19">
         <f t="shared" si="2"/>
         <v>81</v>
@@ -3941,7 +3992,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" s="19">
         <f t="shared" si="2"/>
         <v>82</v>
@@ -3962,7 +4013,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="19">
         <f t="shared" si="2"/>
         <v>83</v>
@@ -3983,7 +4034,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" s="19">
         <f t="shared" si="2"/>
         <v>84</v>
@@ -4004,7 +4055,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" s="19">
         <v>80</v>
       </c>
@@ -4024,7 +4075,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" s="19">
         <f t="shared" si="2"/>
         <v>81</v>
@@ -4045,7 +4096,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="19">
         <f t="shared" si="2"/>
         <v>82</v>
@@ -4066,7 +4117,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" s="19">
         <f t="shared" si="2"/>
         <v>83</v>
@@ -4087,7 +4138,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="19">
         <f t="shared" si="2"/>
         <v>84</v>
@@ -4108,7 +4159,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" s="19">
         <f t="shared" si="2"/>
         <v>85</v>
@@ -4129,7 +4180,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" s="19">
         <v>81</v>
       </c>
@@ -4149,7 +4200,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" s="19">
         <f t="shared" si="2"/>
         <v>82</v>
@@ -4170,7 +4221,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" s="19">
         <f t="shared" si="2"/>
         <v>83</v>
@@ -4191,7 +4242,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" s="19">
         <f t="shared" si="2"/>
         <v>84</v>
@@ -4212,7 +4263,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" s="19">
         <f t="shared" si="2"/>
         <v>85</v>
@@ -4233,7 +4284,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" s="19">
         <f t="shared" si="2"/>
         <v>86</v>
@@ -4254,7 +4305,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="19">
         <v>82</v>
       </c>
@@ -4274,7 +4325,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" s="19">
         <f t="shared" si="2"/>
         <v>83</v>
@@ -4295,7 +4346,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="19">
         <f t="shared" si="2"/>
         <v>84</v>
@@ -4316,7 +4367,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" s="19">
         <f t="shared" si="2"/>
         <v>85</v>
@@ -4337,7 +4388,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" s="19">
         <f t="shared" si="2"/>
         <v>86</v>
@@ -4358,7 +4409,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" s="19">
         <f t="shared" si="2"/>
         <v>87</v>
@@ -4379,7 +4430,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" s="19">
         <v>83</v>
       </c>
@@ -4399,7 +4450,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" s="19">
         <f t="shared" si="2"/>
         <v>84</v>
@@ -4420,7 +4471,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="19">
         <f t="shared" si="2"/>
         <v>85</v>
@@ -4441,7 +4492,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" s="19">
         <f t="shared" si="2"/>
         <v>86</v>
@@ -4462,7 +4513,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" s="19">
         <f t="shared" si="2"/>
         <v>87</v>
@@ -4483,7 +4534,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" s="19">
         <f t="shared" si="2"/>
         <v>88</v>
@@ -4504,7 +4555,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="19">
         <v>84</v>
       </c>
@@ -4524,7 +4575,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" s="19">
         <f t="shared" si="2"/>
         <v>85</v>
@@ -4545,7 +4596,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" s="19">
         <f t="shared" si="2"/>
         <v>86</v>
@@ -4566,7 +4617,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" s="19">
         <f t="shared" si="2"/>
         <v>87</v>
@@ -4587,27 +4638,27 @@
         <v>337</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" s="19">
         <v>88</v>
       </c>
-      <c r="B116" s="27" t="s">
+      <c r="B116" s="19" t="s">
         <v>339</v>
       </c>
-      <c r="C116" s="27" t="s">
+      <c r="C116" s="19" t="s">
         <v>340</v>
       </c>
-      <c r="D116" s="27" t="s">
+      <c r="D116" s="19" t="s">
         <v>341</v>
       </c>
-      <c r="E116" s="28">
+      <c r="E116" s="26">
         <v>46197</v>
       </c>
-      <c r="F116" s="29" t="s">
+      <c r="F116" s="5" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" s="19">
         <f t="shared" si="2"/>
         <v>89</v>
@@ -4628,8 +4679,129 @@
         <v>344</v>
       </c>
     </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A118" s="19">
+        <v>90</v>
+      </c>
+      <c r="B118" s="19" t="s">
+        <v>354</v>
+      </c>
+      <c r="C118" s="19" t="s">
+        <v>346</v>
+      </c>
+      <c r="D118" s="19" t="s">
+        <v>345</v>
+      </c>
+      <c r="E118" s="26">
+        <v>46290</v>
+      </c>
+      <c r="F118" s="5" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A119" s="19">
+        <f t="shared" si="2"/>
+        <v>91</v>
+      </c>
+      <c r="B119" s="19" t="s">
+        <v>354</v>
+      </c>
+      <c r="C119" s="19" t="s">
+        <v>347</v>
+      </c>
+      <c r="D119" s="19" t="s">
+        <v>348</v>
+      </c>
+      <c r="E119" s="26">
+        <v>46290</v>
+      </c>
+      <c r="F119" s="5" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A120" s="19">
+        <v>92</v>
+      </c>
+      <c r="B120" s="19" t="s">
+        <v>354</v>
+      </c>
+      <c r="C120" s="19" t="s">
+        <v>351</v>
+      </c>
+      <c r="D120" s="19" t="s">
+        <v>352</v>
+      </c>
+      <c r="E120" s="26">
+        <v>46290</v>
+      </c>
+      <c r="F120" s="5" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A121" s="19">
+        <v>93</v>
+      </c>
+      <c r="B121" s="19" t="s">
+        <v>354</v>
+      </c>
+      <c r="C121" s="19" t="s">
+        <v>357</v>
+      </c>
+      <c r="D121" s="19" t="s">
+        <v>355</v>
+      </c>
+      <c r="E121" s="26">
+        <v>46291</v>
+      </c>
+      <c r="F121" s="5" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A122" s="19">
+        <v>94</v>
+      </c>
+      <c r="B122" s="19" t="s">
+        <v>354</v>
+      </c>
+      <c r="C122" s="19" t="s">
+        <v>359</v>
+      </c>
+      <c r="D122" s="19" t="s">
+        <v>358</v>
+      </c>
+      <c r="E122" s="26">
+        <v>46291</v>
+      </c>
+      <c r="F122" s="5" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A123" s="19">
+        <v>95</v>
+      </c>
+      <c r="B123" s="19" t="s">
+        <v>354</v>
+      </c>
+      <c r="C123" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="D123" s="19" t="s">
+        <v>362</v>
+      </c>
+      <c r="E123" s="26">
+        <v>46291</v>
+      </c>
+      <c r="F123" s="5" t="s">
+        <v>363</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="D83:D117">
+  <conditionalFormatting sqref="D83:D123">
     <cfRule type="duplicateValues" dxfId="1" priority="6"/>
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
@@ -4640,13 +4812,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{620FB88A-C9C3-47FD-BB4D-39DF868892A8}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>158</v>
       </c>
@@ -4654,7 +4826,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="25" t="s">
         <v>232</v>
       </c>
@@ -4662,7 +4834,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="25" t="s">
         <v>233</v>
       </c>
@@ -4670,7 +4842,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="25" t="s">
         <v>237</v>
       </c>
@@ -4678,7 +4850,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="25" t="s">
         <v>306</v>
       </c>
@@ -4686,7 +4858,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="25" t="s">
         <v>307</v>
       </c>
@@ -4694,7 +4866,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="25" t="s">
         <v>308</v>
       </c>
@@ -4702,7 +4874,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="25" t="s">
         <v>309</v>
       </c>
@@ -4710,7 +4882,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="25" t="s">
         <v>310</v>
       </c>
@@ -4718,7 +4890,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="25" t="s">
         <v>311</v>
       </c>
@@ -4726,7 +4898,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="25" t="s">
         <v>315</v>
       </c>
@@ -4734,7 +4906,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="25" t="s">
         <v>316</v>
       </c>
@@ -4742,7 +4914,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="25" t="s">
         <v>319</v>
       </c>
@@ -4750,7 +4922,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="25" t="s">
         <v>326</v>
       </c>
@@ -4758,7 +4930,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="25" t="s">
         <v>328</v>
       </c>
@@ -4766,7 +4938,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="25" t="s">
         <v>329</v>
       </c>
@@ -4774,7 +4946,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="25" t="s">
         <v>330</v>
       </c>
@@ -4782,7 +4954,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="25" t="s">
         <v>331</v>
       </c>
@@ -4790,7 +4962,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="25" t="s">
         <v>332</v>
       </c>
@@ -4798,7 +4970,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="25" t="s">
         <v>333</v>
       </c>
@@ -4806,7 +4978,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="25" t="s">
         <v>334</v>
       </c>

--- a/Master/KODE DAN RESTO BOM NEW.xlsx
+++ b/Master/KODE DAN RESTO BOM NEW.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24701"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\BAGAS\bacoba\001.DEX\Master\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FORMAT DAN TEMPLATE\T013_Vba_Spit_data\DEX\Master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF1833F-3C68-4EDF-AABC-A5D8F71A9A64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5148890-9C16-4D2B-88AB-3941A5D1F913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{2A27DFF0-1BDB-46C7-8D34-C6B2AB0C8283}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{2A27DFF0-1BDB-46C7-8D34-C6B2AB0C8283}"/>
   </bookViews>
   <sheets>
     <sheet name="KODE" sheetId="1" r:id="rId1"/>
@@ -19,29 +19,20 @@
     <sheet name="EXCLUDE" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">EXCLUDE!$A$1:$B$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">RESTO!$A$1:$F$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">EXCLUDE!$A$1:$C$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">RESTO!$A$1:$F$124</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="367">
   <si>
     <t>NO</t>
   </si>
@@ -1133,6 +1124,15 @@
   </si>
   <si>
     <t>1314.KPNSUD</t>
+  </si>
+  <si>
+    <t>MLGDIR</t>
+  </si>
+  <si>
+    <t>1106.1-G.Malang - Dirgantara (MLGDIR)</t>
+  </si>
+  <si>
+    <t>1106.MLGDIR</t>
   </si>
 </sst>
 </file>
@@ -1190,7 +1190,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1275,6 +1275,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -1345,7 +1351,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1419,6 +1425,13 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="15" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1477,6 +1490,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFFF00"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1786,14 +1804,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04EABAD4-117C-4DE8-B838-BB6A4F70CD80}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>156</v>
       </c>
@@ -1801,7 +1819,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
         <v>550064</v>
       </c>
@@ -1809,7 +1827,7 @@
         <v>550364</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="14">
         <v>550065</v>
       </c>
@@ -1817,7 +1835,7 @@
         <v>550365</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="14">
         <v>550080</v>
       </c>
@@ -1825,7 +1843,7 @@
         <v>550366</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="14">
         <v>550081</v>
       </c>
@@ -1833,7 +1851,7 @@
         <v>550367</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="14">
         <v>550260</v>
       </c>
@@ -1841,7 +1859,7 @@
         <v>550368</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="14">
         <v>550261</v>
       </c>
@@ -1849,7 +1867,7 @@
         <v>550369</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="14">
         <v>550262</v>
       </c>
@@ -1857,7 +1875,7 @@
         <v>550370</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
         <v>550263</v>
       </c>
@@ -1865,7 +1883,7 @@
         <v>550371</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="14">
         <v>550264</v>
       </c>
@@ -1873,7 +1891,7 @@
         <v>550372</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
         <v>550265</v>
       </c>
@@ -1881,7 +1899,7 @@
         <v>550373</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="14">
         <v>550266</v>
       </c>
@@ -1889,7 +1907,7 @@
         <v>550374</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
         <v>550267</v>
       </c>
@@ -1897,7 +1915,7 @@
         <v>550375</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="14">
         <v>550268</v>
       </c>
@@ -1905,7 +1923,7 @@
         <v>550376</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="14">
         <v>550269</v>
       </c>
@@ -1913,7 +1931,7 @@
         <v>550377</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="14">
         <v>550270</v>
       </c>
@@ -1921,7 +1939,7 @@
         <v>550378</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14">
         <v>550271</v>
       </c>
@@ -1929,7 +1947,7 @@
         <v>550379</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="14">
         <v>550146</v>
       </c>
@@ -1937,7 +1955,7 @@
         <v>550430</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="14">
         <v>550151</v>
       </c>
@@ -1945,7 +1963,7 @@
         <v>550431</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
         <v>550152</v>
       </c>
@@ -1953,7 +1971,7 @@
         <v>550432</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="14">
         <v>550153</v>
       </c>
@@ -1961,7 +1979,7 @@
         <v>550433</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="14">
         <v>550154</v>
       </c>
@@ -1978,15 +1996,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB90F88C-CAFF-4807-B167-4FE3417BBD55}">
   <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.453125" customWidth="1"/>
-    <col min="3" max="3" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>158</v>
       </c>
@@ -2000,202 +2018,202 @@
         <v>157</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B2" s="4"/>
       <c r="C2" s="23"/>
       <c r="D2" s="23"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B3" s="4"/>
       <c r="C3" s="23"/>
       <c r="D3" s="23"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B4" s="4"/>
       <c r="C4" s="23"/>
       <c r="D4" s="23"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B5" s="4"/>
       <c r="C5" s="23"/>
       <c r="D5" s="23"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B6" s="4"/>
       <c r="C6" s="23"/>
       <c r="D6" s="23"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B7" s="4"/>
       <c r="C7" s="23"/>
       <c r="D7" s="23"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B8" s="4"/>
       <c r="C8" s="23"/>
       <c r="D8" s="23"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B9" s="4"/>
       <c r="C9" s="23"/>
       <c r="D9" s="23"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B10" s="4"/>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B11" s="4"/>
       <c r="C11" s="23"/>
       <c r="D11" s="23"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B12" s="4"/>
       <c r="C12" s="23"/>
       <c r="D12" s="23"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B13" s="4"/>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B14" s="4"/>
       <c r="C14" s="23"/>
       <c r="D14" s="23"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B15" s="4"/>
       <c r="C15" s="23"/>
       <c r="D15" s="23"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B16" s="4"/>
       <c r="C16" s="23"/>
       <c r="D16" s="23"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="4"/>
       <c r="C17" s="23"/>
       <c r="D17" s="23"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="4"/>
       <c r="C18" s="23"/>
       <c r="D18" s="23"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="4"/>
       <c r="C19" s="23"/>
       <c r="D19" s="23"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="4"/>
       <c r="C20" s="23"/>
       <c r="D20" s="23"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="4"/>
       <c r="C21" s="23"/>
       <c r="D21" s="23"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" s="4"/>
       <c r="C22" s="23"/>
       <c r="D22" s="23"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" s="4"/>
       <c r="C23" s="23"/>
       <c r="D23" s="23"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24" s="4"/>
       <c r="C24" s="23"/>
       <c r="D24" s="23"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25" s="4"/>
       <c r="C25" s="23"/>
       <c r="D25" s="23"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26" s="4"/>
       <c r="C26" s="23"/>
       <c r="D26" s="23"/>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27" s="4"/>
       <c r="C27" s="23"/>
       <c r="D27" s="23"/>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28" s="4"/>
       <c r="C28" s="23"/>
       <c r="D28" s="23"/>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29" s="4"/>
       <c r="C29" s="23"/>
       <c r="D29" s="23"/>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="4"/>
       <c r="C30" s="23"/>
       <c r="D30" s="23"/>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B31" s="4"/>
       <c r="C31" s="23"/>
       <c r="D31" s="23"/>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32" s="4"/>
       <c r="C32" s="23"/>
       <c r="D32" s="23"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" s="4"/>
       <c r="C33" s="23"/>
       <c r="D33" s="23"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" s="4"/>
       <c r="C34" s="23"/>
       <c r="D34" s="23"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35" s="4"/>
       <c r="C35" s="23"/>
       <c r="D35" s="23"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B36" s="4"/>
       <c r="C36" s="23"/>
       <c r="D36" s="23"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B37" s="4"/>
       <c r="C37" s="23"/>
       <c r="D37" s="23"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B38" s="4"/>
       <c r="C38" s="23"/>
       <c r="D38" s="23"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B39" s="4"/>
       <c r="C39" s="23"/>
       <c r="D39" s="23"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B40" s="4"/>
       <c r="C40" s="23"/>
       <c r="D40" s="23"/>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B41" s="4"/>
       <c r="C41" s="23"/>
       <c r="D41" s="23"/>
@@ -2216,17 +2234,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0933A7F-4C29-4A64-8B36-B4F9E885B333}">
-  <dimension ref="A1:F123"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:F124"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="41.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2246,7 +2264,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -2266,7 +2284,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <f t="shared" ref="A3:A51" si="0">1+A2</f>
         <v>2</v>
@@ -2287,7 +2305,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2308,7 +2326,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2329,7 +2347,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2350,7 +2368,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2371,7 +2389,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2392,7 +2410,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2413,7 +2431,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2434,7 +2452,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2455,7 +2473,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2476,7 +2494,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2497,7 +2515,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2518,7 +2536,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2539,7 +2557,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2560,7 +2578,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2581,7 +2599,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2602,7 +2620,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2623,7 +2641,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2644,7 +2662,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2665,7 +2683,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2686,7 +2704,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -2707,7 +2725,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -2728,7 +2746,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2749,7 +2767,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -2770,7 +2788,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -2791,7 +2809,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -2812,7 +2830,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -2833,7 +2851,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -2854,7 +2872,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -2875,7 +2893,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -2896,7 +2914,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -2917,7 +2935,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -2938,7 +2956,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -2959,7 +2977,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -2980,7 +2998,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -3001,7 +3019,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -3022,7 +3040,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -3043,7 +3061,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -3064,7 +3082,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -3085,7 +3103,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -3106,7 +3124,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -3127,7 +3145,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -3148,7 +3166,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -3169,7 +3187,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -3190,7 +3208,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -3211,7 +3229,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -3232,7 +3250,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -3253,7 +3271,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -3274,7 +3292,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -3295,7 +3313,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -3315,7 +3333,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -3336,7 +3354,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -3357,7 +3375,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -3378,7 +3396,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -3399,7 +3417,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -3420,7 +3438,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -3441,7 +3459,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -3462,7 +3480,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -3483,7 +3501,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -3504,7 +3522,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -3525,7 +3543,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -3546,7 +3564,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="17">
         <f>1+A61</f>
         <v>61</v>
@@ -3568,7 +3586,7 @@
         <v>1053.BGRPAD</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="19">
         <f t="shared" ref="A65:A119" si="2">1+A64</f>
         <v>62</v>
@@ -3590,7 +3608,7 @@
         <v>1074.BGRTAJ</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="19">
         <f t="shared" si="2"/>
         <v>63</v>
@@ -3612,7 +3630,7 @@
         <v>1079.BGRSAP</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="19">
         <f t="shared" si="2"/>
         <v>64</v>
@@ -3634,7 +3652,7 @@
         <v>1100.BGRABD</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="19">
         <f t="shared" si="2"/>
         <v>65</v>
@@ -3656,7 +3674,7 @@
         <v>1112.BGRSHO</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="19">
         <f t="shared" si="2"/>
         <v>66</v>
@@ -3678,7 +3696,7 @@
         <v>1190.BGRBAT</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="19">
         <f t="shared" si="2"/>
         <v>67</v>
@@ -3699,7 +3717,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="19">
         <f t="shared" si="2"/>
         <v>68</v>
@@ -3720,7 +3738,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="19">
         <f t="shared" si="2"/>
         <v>69</v>
@@ -3741,7 +3759,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="19">
         <f t="shared" si="2"/>
         <v>70</v>
@@ -3762,7 +3780,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="19">
         <f t="shared" si="2"/>
         <v>71</v>
@@ -3783,7 +3801,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="19">
         <f t="shared" si="2"/>
         <v>72</v>
@@ -3804,7 +3822,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="19">
         <f t="shared" si="2"/>
         <v>73</v>
@@ -3825,7 +3843,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="19">
         <f t="shared" si="2"/>
         <v>74</v>
@@ -3846,7 +3864,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="19">
         <f t="shared" si="2"/>
         <v>75</v>
@@ -3867,7 +3885,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="19">
         <f t="shared" si="2"/>
         <v>76</v>
@@ -3888,7 +3906,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="19">
         <f t="shared" si="2"/>
         <v>77</v>
@@ -3903,13 +3921,13 @@
         <v>219</v>
       </c>
       <c r="E80" s="4">
-        <v>46175</v>
-      </c>
-      <c r="F80" s="25" t="s">
+        <v>46302</v>
+      </c>
+      <c r="F80" s="27" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="19">
         <f t="shared" si="2"/>
         <v>78</v>
@@ -3924,13 +3942,13 @@
         <v>221</v>
       </c>
       <c r="E81" s="4">
-        <v>46175</v>
-      </c>
-      <c r="F81" s="25" t="s">
+        <v>46302</v>
+      </c>
+      <c r="F81" s="27" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="19">
         <v>79</v>
       </c>
@@ -3944,13 +3962,13 @@
         <v>236</v>
       </c>
       <c r="E82" s="4">
-        <v>46204</v>
-      </c>
-      <c r="F82" s="25" t="s">
+        <v>46304</v>
+      </c>
+      <c r="F82" s="27" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="19">
         <f t="shared" si="2"/>
         <v>80</v>
@@ -3971,7 +3989,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="19">
         <f t="shared" si="2"/>
         <v>81</v>
@@ -3986,13 +4004,13 @@
         <v>242</v>
       </c>
       <c r="E84" s="4">
-        <v>46212</v>
-      </c>
-      <c r="F84" s="25" t="s">
+        <v>46302</v>
+      </c>
+      <c r="F84" s="27" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="19">
         <f t="shared" si="2"/>
         <v>82</v>
@@ -4007,13 +4025,13 @@
         <v>244</v>
       </c>
       <c r="E85" s="4">
-        <v>46212</v>
-      </c>
-      <c r="F85" s="25" t="s">
+        <v>46302</v>
+      </c>
+      <c r="F85" s="27" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="19">
         <f t="shared" si="2"/>
         <v>83</v>
@@ -4028,13 +4046,13 @@
         <v>246</v>
       </c>
       <c r="E86" s="4">
-        <v>46212</v>
-      </c>
-      <c r="F86" s="25" t="s">
+        <v>46302</v>
+      </c>
+      <c r="F86" s="27" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="19">
         <f t="shared" si="2"/>
         <v>84</v>
@@ -4049,13 +4067,13 @@
         <v>248</v>
       </c>
       <c r="E87" s="4">
-        <v>46212</v>
-      </c>
-      <c r="F87" s="25" t="s">
+        <v>46302</v>
+      </c>
+      <c r="F87" s="27" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="19">
         <v>80</v>
       </c>
@@ -4069,13 +4087,13 @@
         <v>250</v>
       </c>
       <c r="E88" s="4">
-        <v>46212</v>
-      </c>
-      <c r="F88" s="25" t="s">
+        <v>46302</v>
+      </c>
+      <c r="F88" s="27" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="19">
         <f t="shared" si="2"/>
         <v>81</v>
@@ -4090,13 +4108,13 @@
         <v>252</v>
       </c>
       <c r="E89" s="4">
-        <v>46212</v>
-      </c>
-      <c r="F89" s="25" t="s">
+        <v>46302</v>
+      </c>
+      <c r="F89" s="27" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="19">
         <f t="shared" si="2"/>
         <v>82</v>
@@ -4117,7 +4135,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="19">
         <f t="shared" si="2"/>
         <v>83</v>
@@ -4138,7 +4156,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="19">
         <f t="shared" si="2"/>
         <v>84</v>
@@ -4159,7 +4177,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="19">
         <f t="shared" si="2"/>
         <v>85</v>
@@ -4174,13 +4192,13 @@
         <v>260</v>
       </c>
       <c r="E93" s="4">
-        <v>46212</v>
-      </c>
-      <c r="F93" s="25" t="s">
+        <v>46301</v>
+      </c>
+      <c r="F93" s="27" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="19">
         <v>81</v>
       </c>
@@ -4200,7 +4218,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="19">
         <f t="shared" si="2"/>
         <v>82</v>
@@ -4221,7 +4239,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="19">
         <f t="shared" si="2"/>
         <v>83</v>
@@ -4242,7 +4260,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="19">
         <f t="shared" si="2"/>
         <v>84</v>
@@ -4263,7 +4281,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="19">
         <f t="shared" si="2"/>
         <v>85</v>
@@ -4284,7 +4302,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="19">
         <f t="shared" si="2"/>
         <v>86</v>
@@ -4305,7 +4323,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="19">
         <v>82</v>
       </c>
@@ -4325,7 +4343,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="19">
         <f t="shared" si="2"/>
         <v>83</v>
@@ -4346,7 +4364,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="19">
         <f t="shared" si="2"/>
         <v>84</v>
@@ -4367,7 +4385,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="19">
         <f t="shared" si="2"/>
         <v>85</v>
@@ -4388,7 +4406,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="19">
         <f t="shared" si="2"/>
         <v>86</v>
@@ -4409,7 +4427,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="19">
         <f t="shared" si="2"/>
         <v>87</v>
@@ -4430,7 +4448,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="19">
         <v>83</v>
       </c>
@@ -4450,7 +4468,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="19">
         <f t="shared" si="2"/>
         <v>84</v>
@@ -4471,7 +4489,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="19">
         <f t="shared" si="2"/>
         <v>85</v>
@@ -4492,7 +4510,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="19">
         <f t="shared" si="2"/>
         <v>86</v>
@@ -4513,7 +4531,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="19">
         <f t="shared" si="2"/>
         <v>87</v>
@@ -4534,7 +4552,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="19">
         <f t="shared" si="2"/>
         <v>88</v>
@@ -4555,7 +4573,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="19">
         <v>84</v>
       </c>
@@ -4575,7 +4593,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="19">
         <f t="shared" si="2"/>
         <v>85</v>
@@ -4596,7 +4614,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="19">
         <f t="shared" si="2"/>
         <v>86</v>
@@ -4617,7 +4635,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="19">
         <f t="shared" si="2"/>
         <v>87</v>
@@ -4638,7 +4656,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="19">
         <v>88</v>
       </c>
@@ -4658,7 +4676,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="19">
         <f t="shared" si="2"/>
         <v>89</v>
@@ -4679,7 +4697,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="19">
         <v>90</v>
       </c>
@@ -4699,7 +4717,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="19">
         <f t="shared" si="2"/>
         <v>91</v>
@@ -4720,7 +4738,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="19">
         <v>92</v>
       </c>
@@ -4740,7 +4758,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="19">
         <v>93</v>
       </c>
@@ -4760,7 +4778,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="19">
         <v>94</v>
       </c>
@@ -4780,7 +4798,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="19">
         <v>95</v>
       </c>
@@ -4800,8 +4818,28 @@
         <v>363</v>
       </c>
     </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="19">
+        <v>96</v>
+      </c>
+      <c r="B124" s="28" t="s">
+        <v>354</v>
+      </c>
+      <c r="C124" s="28" t="s">
+        <v>364</v>
+      </c>
+      <c r="D124" s="28" t="s">
+        <v>365</v>
+      </c>
+      <c r="E124" s="29">
+        <v>46302</v>
+      </c>
+      <c r="F124" s="27" t="s">
+        <v>366</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="D83:D123">
+  <conditionalFormatting sqref="D83:D124">
     <cfRule type="duplicateValues" dxfId="1" priority="6"/>
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
@@ -4811,14 +4849,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{620FB88A-C9C3-47FD-BB4D-39DF868892A8}">
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>158</v>
       </c>
@@ -4826,167 +4864,88 @@
         <v>338</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
-        <v>232</v>
+        <v>316</v>
       </c>
       <c r="B2" s="4">
         <v>46218</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
-        <v>233</v>
+        <v>319</v>
       </c>
       <c r="B3" s="4">
         <v>46218</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
-        <v>237</v>
+        <v>326</v>
       </c>
       <c r="B4" s="4">
         <v>46218</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="25" t="s">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="B5" s="4">
         <v>46218</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="B6" s="4">
         <v>46218</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="25" t="s">
-        <v>308</v>
+        <v>330</v>
       </c>
       <c r="B7" s="4">
         <v>46218</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c r="B8" s="4">
         <v>46218</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="25" t="s">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="B9" s="4">
         <v>46218</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="B10" s="4">
         <v>46218</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="25" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="B11" s="4">
         <v>46218</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="25" t="s">
-        <v>316</v>
-      </c>
-      <c r="B12" s="4">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="25" t="s">
-        <v>319</v>
-      </c>
-      <c r="B13" s="4">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="25" t="s">
-        <v>326</v>
-      </c>
-      <c r="B14" s="4">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="25" t="s">
-        <v>328</v>
-      </c>
-      <c r="B15" s="4">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="25" t="s">
-        <v>329</v>
-      </c>
-      <c r="B16" s="4">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="25" t="s">
-        <v>330</v>
-      </c>
-      <c r="B17" s="4">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="25" t="s">
-        <v>331</v>
-      </c>
-      <c r="B18" s="4">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" s="25" t="s">
-        <v>332</v>
-      </c>
-      <c r="B19" s="4">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" s="25" t="s">
-        <v>333</v>
-      </c>
-      <c r="B20" s="4">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" s="25" t="s">
-        <v>334</v>
-      </c>
-      <c r="B21" s="4">
-        <v>46218</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:C11" xr:uid="{620FB88A-C9C3-47FD-BB4D-39DF868892A8}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Master/KODE DAN RESTO BOM NEW.xlsx
+++ b/Master/KODE DAN RESTO BOM NEW.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FORMAT DAN TEMPLATE\T013_Vba_Spit_data\DEX\Master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5148890-9C16-4D2B-88AB-3941A5D1F913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D76E1CD0-CAC6-48A8-AD2A-17E20736EEFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{2A27DFF0-1BDB-46C7-8D34-C6B2AB0C8283}"/>
   </bookViews>
@@ -19,8 +19,8 @@
     <sheet name="EXCLUDE" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">EXCLUDE!$A$1:$C$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">RESTO!$A$1:$F$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">EXCLUDE!$A$1:$C$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">RESTO!$A$1:$F$126</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="373">
   <si>
     <t>NO</t>
   </si>
@@ -1133,6 +1133,24 @@
   </si>
   <si>
     <t>1106.MLGDIR</t>
+  </si>
+  <si>
+    <t>KWGWAR</t>
+  </si>
+  <si>
+    <t>1383.1-G.Karawang - Warudoyong Utara (KWGWAR)</t>
+  </si>
+  <si>
+    <t>TGRKEL</t>
+  </si>
+  <si>
+    <t>1383.KWGWAR</t>
+  </si>
+  <si>
+    <t>1386.1-G.Tangerang - Raya Kelapa Dua (TGRKEL)</t>
+  </si>
+  <si>
+    <t>1386.TGRKEL</t>
   </si>
 </sst>
 </file>
@@ -1190,7 +1208,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1281,6 +1299,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -1351,7 +1375,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1432,6 +1456,7 @@
     <xf numFmtId="14" fontId="3" fillId="15" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2234,7 +2259,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0933A7F-4C29-4A64-8B36-B4F9E885B333}">
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F126"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
@@ -4212,9 +4237,9 @@
         <v>262</v>
       </c>
       <c r="E94" s="4">
-        <v>46212</v>
-      </c>
-      <c r="F94" s="25" t="s">
+        <v>46317</v>
+      </c>
+      <c r="F94" s="30" t="s">
         <v>316</v>
       </c>
     </row>
@@ -4275,9 +4300,9 @@
         <v>268</v>
       </c>
       <c r="E97" s="4">
-        <v>46212</v>
-      </c>
-      <c r="F97" s="25" t="s">
+        <v>46315</v>
+      </c>
+      <c r="F97" s="30" t="s">
         <v>319</v>
       </c>
     </row>
@@ -4421,9 +4446,9 @@
         <v>282</v>
       </c>
       <c r="E104" s="4">
-        <v>46212</v>
-      </c>
-      <c r="F104" s="25" t="s">
+        <v>46315</v>
+      </c>
+      <c r="F104" s="30" t="s">
         <v>326</v>
       </c>
     </row>
@@ -4462,9 +4487,9 @@
         <v>286</v>
       </c>
       <c r="E106" s="4">
-        <v>46212</v>
-      </c>
-      <c r="F106" s="25" t="s">
+        <v>46317</v>
+      </c>
+      <c r="F106" s="30" t="s">
         <v>328</v>
       </c>
     </row>
@@ -4483,9 +4508,9 @@
         <v>288</v>
       </c>
       <c r="E107" s="4">
-        <v>46212</v>
-      </c>
-      <c r="F107" s="25" t="s">
+        <v>46315</v>
+      </c>
+      <c r="F107" s="30" t="s">
         <v>329</v>
       </c>
     </row>
@@ -4504,9 +4529,9 @@
         <v>290</v>
       </c>
       <c r="E108" s="4">
-        <v>46212</v>
-      </c>
-      <c r="F108" s="25" t="s">
+        <v>46317</v>
+      </c>
+      <c r="F108" s="30" t="s">
         <v>330</v>
       </c>
     </row>
@@ -4525,9 +4550,9 @@
         <v>292</v>
       </c>
       <c r="E109" s="4">
-        <v>46212</v>
-      </c>
-      <c r="F109" s="25" t="s">
+        <v>46317</v>
+      </c>
+      <c r="F109" s="30" t="s">
         <v>331</v>
       </c>
     </row>
@@ -4546,9 +4571,9 @@
         <v>294</v>
       </c>
       <c r="E110" s="4">
-        <v>46212</v>
-      </c>
-      <c r="F110" s="25" t="s">
+        <v>46318</v>
+      </c>
+      <c r="F110" s="30" t="s">
         <v>332</v>
       </c>
     </row>
@@ -4567,9 +4592,9 @@
         <v>296</v>
       </c>
       <c r="E111" s="4">
-        <v>46212</v>
-      </c>
-      <c r="F111" s="25" t="s">
+        <v>46318</v>
+      </c>
+      <c r="F111" s="30" t="s">
         <v>333</v>
       </c>
     </row>
@@ -4587,9 +4612,9 @@
         <v>298</v>
       </c>
       <c r="E112" s="4">
-        <v>46212</v>
-      </c>
-      <c r="F112" s="25" t="s">
+        <v>46315</v>
+      </c>
+      <c r="F112" s="30" t="s">
         <v>334</v>
       </c>
     </row>
@@ -4838,8 +4863,49 @@
         <v>366</v>
       </c>
     </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="19">
+        <v>97</v>
+      </c>
+      <c r="B125" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C125" s="19" t="s">
+        <v>367</v>
+      </c>
+      <c r="D125" s="19" t="s">
+        <v>368</v>
+      </c>
+      <c r="E125" s="26">
+        <v>46317</v>
+      </c>
+      <c r="F125" s="5" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="19">
+        <v>98</v>
+      </c>
+      <c r="B126" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C126" s="19" t="s">
+        <v>369</v>
+      </c>
+      <c r="D126" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="E126" s="26">
+        <v>46317</v>
+      </c>
+      <c r="F126" s="5" t="s">
+        <v>372</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="D83:D124">
+  <autoFilter ref="A1:F126" xr:uid="{C0933A7F-4C29-4A64-8B36-B4F9E885B333}"/>
+  <conditionalFormatting sqref="D83:D126">
     <cfRule type="duplicateValues" dxfId="1" priority="6"/>
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
@@ -4849,7 +4915,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{620FB88A-C9C3-47FD-BB4D-39DF868892A8}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:F126"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
@@ -4864,88 +4930,12 @@
         <v>338</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
-        <v>316</v>
-      </c>
-      <c r="B2" s="4">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
-        <v>319</v>
-      </c>
-      <c r="B3" s="4">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="25" t="s">
-        <v>326</v>
-      </c>
-      <c r="B4" s="4">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="25" t="s">
-        <v>328</v>
-      </c>
-      <c r="B5" s="4">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="25" t="s">
-        <v>329</v>
-      </c>
-      <c r="B6" s="4">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="25" t="s">
-        <v>330</v>
-      </c>
-      <c r="B7" s="4">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="25" t="s">
-        <v>331</v>
-      </c>
-      <c r="B8" s="4">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="25" t="s">
-        <v>332</v>
-      </c>
-      <c r="B9" s="4">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="25" t="s">
-        <v>333</v>
-      </c>
-      <c r="B10" s="4">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="25" t="s">
-        <v>334</v>
-      </c>
-      <c r="B11" s="4">
-        <v>46218</v>
+    <row r="126" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F126" t="s">
+        <v>372</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C11" xr:uid="{620FB88A-C9C3-47FD-BB4D-39DF868892A8}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Master/KODE DAN RESTO BOM NEW.xlsx
+++ b/Master/KODE DAN RESTO BOM NEW.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FORMAT DAN TEMPLATE\T013_Vba_Spit_data\DEX\Master\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder\Flowbit\DEX v2.0.1\Master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D76E1CD0-CAC6-48A8-AD2A-17E20736EEFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A484E7B4-D8EA-48A4-8523-4C166D4B3E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{2A27DFF0-1BDB-46C7-8D34-C6B2AB0C8283}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{2A27DFF0-1BDB-46C7-8D34-C6B2AB0C8283}"/>
   </bookViews>
   <sheets>
     <sheet name="KODE" sheetId="1" r:id="rId1"/>
@@ -27,12 +27,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="373">
   <si>
     <t>NO</t>
   </si>
@@ -1532,9 +1543,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1572,7 +1583,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1678,7 +1689,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1820,7 +1831,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1829,14 +1840,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04EABAD4-117C-4DE8-B838-BB6A4F70CD80}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
         <v>156</v>
       </c>
@@ -1844,7 +1855,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="14">
         <v>550064</v>
       </c>
@@ -1852,7 +1863,7 @@
         <v>550364</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="14">
         <v>550065</v>
       </c>
@@ -1860,7 +1871,7 @@
         <v>550365</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="14">
         <v>550080</v>
       </c>
@@ -1868,7 +1879,7 @@
         <v>550366</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="14">
         <v>550081</v>
       </c>
@@ -1876,7 +1887,7 @@
         <v>550367</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="14">
         <v>550260</v>
       </c>
@@ -1884,7 +1895,7 @@
         <v>550368</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="14">
         <v>550261</v>
       </c>
@@ -1892,7 +1903,7 @@
         <v>550369</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="14">
         <v>550262</v>
       </c>
@@ -1900,7 +1911,7 @@
         <v>550370</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="14">
         <v>550263</v>
       </c>
@@ -1908,7 +1919,7 @@
         <v>550371</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="14">
         <v>550264</v>
       </c>
@@ -1916,7 +1927,7 @@
         <v>550372</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="14">
         <v>550265</v>
       </c>
@@ -1924,7 +1935,7 @@
         <v>550373</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="14">
         <v>550266</v>
       </c>
@@ -1932,7 +1943,7 @@
         <v>550374</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="14">
         <v>550267</v>
       </c>
@@ -1940,7 +1951,7 @@
         <v>550375</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="14">
         <v>550268</v>
       </c>
@@ -1948,7 +1959,7 @@
         <v>550376</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="14">
         <v>550269</v>
       </c>
@@ -1956,7 +1967,7 @@
         <v>550377</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="14">
         <v>550270</v>
       </c>
@@ -1964,7 +1975,7 @@
         <v>550378</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="14">
         <v>550271</v>
       </c>
@@ -1972,7 +1983,7 @@
         <v>550379</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="14">
         <v>550146</v>
       </c>
@@ -1980,7 +1991,7 @@
         <v>550430</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="14">
         <v>550151</v>
       </c>
@@ -1988,7 +1999,7 @@
         <v>550431</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="14">
         <v>550152</v>
       </c>
@@ -1996,7 +2007,7 @@
         <v>550432</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="14">
         <v>550153</v>
       </c>
@@ -2004,7 +2015,7 @@
         <v>550433</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="14">
         <v>550154</v>
       </c>
@@ -2021,15 +2032,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB90F88C-CAFF-4807-B167-4FE3417BBD55}">
   <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" customWidth="1"/>
+    <col min="3" max="3" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
         <v>158</v>
       </c>
@@ -2043,202 +2054,202 @@
         <v>157</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B2" s="4"/>
       <c r="C2" s="23"/>
       <c r="D2" s="23"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B3" s="4"/>
       <c r="C3" s="23"/>
       <c r="D3" s="23"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B4" s="4"/>
       <c r="C4" s="23"/>
       <c r="D4" s="23"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B5" s="4"/>
       <c r="C5" s="23"/>
       <c r="D5" s="23"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B6" s="4"/>
       <c r="C6" s="23"/>
       <c r="D6" s="23"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B7" s="4"/>
       <c r="C7" s="23"/>
       <c r="D7" s="23"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B8" s="4"/>
       <c r="C8" s="23"/>
       <c r="D8" s="23"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B9" s="4"/>
       <c r="C9" s="23"/>
       <c r="D9" s="23"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B10" s="4"/>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B11" s="4"/>
       <c r="C11" s="23"/>
       <c r="D11" s="23"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B12" s="4"/>
       <c r="C12" s="23"/>
       <c r="D12" s="23"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B13" s="4"/>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B14" s="4"/>
       <c r="C14" s="23"/>
       <c r="D14" s="23"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B15" s="4"/>
       <c r="C15" s="23"/>
       <c r="D15" s="23"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B16" s="4"/>
       <c r="C16" s="23"/>
       <c r="D16" s="23"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B17" s="4"/>
       <c r="C17" s="23"/>
       <c r="D17" s="23"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B18" s="4"/>
       <c r="C18" s="23"/>
       <c r="D18" s="23"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B19" s="4"/>
       <c r="C19" s="23"/>
       <c r="D19" s="23"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B20" s="4"/>
       <c r="C20" s="23"/>
       <c r="D20" s="23"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B21" s="4"/>
       <c r="C21" s="23"/>
       <c r="D21" s="23"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B22" s="4"/>
       <c r="C22" s="23"/>
       <c r="D22" s="23"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B23" s="4"/>
       <c r="C23" s="23"/>
       <c r="D23" s="23"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B24" s="4"/>
       <c r="C24" s="23"/>
       <c r="D24" s="23"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B25" s="4"/>
       <c r="C25" s="23"/>
       <c r="D25" s="23"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B26" s="4"/>
       <c r="C26" s="23"/>
       <c r="D26" s="23"/>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B27" s="4"/>
       <c r="C27" s="23"/>
       <c r="D27" s="23"/>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B28" s="4"/>
       <c r="C28" s="23"/>
       <c r="D28" s="23"/>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B29" s="4"/>
       <c r="C29" s="23"/>
       <c r="D29" s="23"/>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B30" s="4"/>
       <c r="C30" s="23"/>
       <c r="D30" s="23"/>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B31" s="4"/>
       <c r="C31" s="23"/>
       <c r="D31" s="23"/>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B32" s="4"/>
       <c r="C32" s="23"/>
       <c r="D32" s="23"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B33" s="4"/>
       <c r="C33" s="23"/>
       <c r="D33" s="23"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B34" s="4"/>
       <c r="C34" s="23"/>
       <c r="D34" s="23"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B35" s="4"/>
       <c r="C35" s="23"/>
       <c r="D35" s="23"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B36" s="4"/>
       <c r="C36" s="23"/>
       <c r="D36" s="23"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B37" s="4"/>
       <c r="C37" s="23"/>
       <c r="D37" s="23"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B38" s="4"/>
       <c r="C38" s="23"/>
       <c r="D38" s="23"/>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B39" s="4"/>
       <c r="C39" s="23"/>
       <c r="D39" s="23"/>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B40" s="4"/>
       <c r="C40" s="23"/>
       <c r="D40" s="23"/>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B41" s="4"/>
       <c r="C41" s="23"/>
       <c r="D41" s="23"/>
@@ -2260,16 +2271,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0933A7F-4C29-4A64-8B36-B4F9E885B333}">
   <dimension ref="A1:F126"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="41.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2289,7 +2300,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -2309,7 +2320,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <f t="shared" ref="A3:A51" si="0">1+A2</f>
         <v>2</v>
@@ -2330,7 +2341,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2351,7 +2362,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2372,7 +2383,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2393,7 +2404,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2414,7 +2425,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2435,7 +2446,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2456,7 +2467,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2477,7 +2488,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2498,7 +2509,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2519,7 +2530,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2540,7 +2551,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2561,7 +2572,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2582,7 +2593,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2603,7 +2614,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2624,7 +2635,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2645,7 +2656,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2666,7 +2677,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2687,7 +2698,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2708,7 +2719,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2729,7 +2740,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -2750,7 +2761,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -2771,7 +2782,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2792,7 +2803,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -2813,7 +2824,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -2834,7 +2845,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -2855,7 +2866,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -2876,7 +2887,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -2897,7 +2908,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -2918,7 +2929,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -2939,7 +2950,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -2960,7 +2971,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -2981,7 +2992,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -3002,7 +3013,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -3023,7 +3034,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -3044,7 +3055,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -3065,7 +3076,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -3086,7 +3097,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -3107,7 +3118,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -3128,7 +3139,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -3149,7 +3160,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -3170,7 +3181,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -3191,7 +3202,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -3212,7 +3223,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -3233,7 +3244,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -3254,7 +3265,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -3275,7 +3286,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -3296,7 +3307,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -3317,7 +3328,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -3338,7 +3349,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -3358,7 +3369,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -3379,7 +3390,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -3400,7 +3411,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -3421,7 +3432,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -3442,7 +3453,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -3463,7 +3474,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -3484,7 +3495,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -3505,7 +3516,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -3526,7 +3537,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -3547,7 +3558,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -3568,7 +3579,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -3589,7 +3600,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="17">
         <f>1+A61</f>
         <v>61</v>
@@ -3611,7 +3622,7 @@
         <v>1053.BGRPAD</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="19">
         <f t="shared" ref="A65:A119" si="2">1+A64</f>
         <v>62</v>
@@ -3633,7 +3644,7 @@
         <v>1074.BGRTAJ</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="19">
         <f t="shared" si="2"/>
         <v>63</v>
@@ -3655,7 +3666,7 @@
         <v>1079.BGRSAP</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="19">
         <f t="shared" si="2"/>
         <v>64</v>
@@ -3677,7 +3688,7 @@
         <v>1100.BGRABD</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="19">
         <f t="shared" si="2"/>
         <v>65</v>
@@ -3699,7 +3710,7 @@
         <v>1112.BGRSHO</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="19">
         <f t="shared" si="2"/>
         <v>66</v>
@@ -3721,7 +3732,7 @@
         <v>1190.BGRBAT</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="19">
         <f t="shared" si="2"/>
         <v>67</v>
@@ -3742,7 +3753,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="19">
         <f t="shared" si="2"/>
         <v>68</v>
@@ -3763,7 +3774,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="19">
         <f t="shared" si="2"/>
         <v>69</v>
@@ -3784,7 +3795,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="19">
         <f t="shared" si="2"/>
         <v>70</v>
@@ -3805,7 +3816,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="19">
         <f t="shared" si="2"/>
         <v>71</v>
@@ -3826,7 +3837,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="19">
         <f t="shared" si="2"/>
         <v>72</v>
@@ -3847,7 +3858,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="19">
         <f t="shared" si="2"/>
         <v>73</v>
@@ -3868,7 +3879,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="19">
         <f t="shared" si="2"/>
         <v>74</v>
@@ -3889,7 +3900,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="19">
         <f t="shared" si="2"/>
         <v>75</v>
@@ -3910,7 +3921,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="19">
         <f t="shared" si="2"/>
         <v>76</v>
@@ -3931,7 +3942,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="19">
         <f t="shared" si="2"/>
         <v>77</v>
@@ -3952,7 +3963,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="19">
         <f t="shared" si="2"/>
         <v>78</v>
@@ -3973,7 +3984,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="19">
         <v>79</v>
       </c>
@@ -3993,7 +4004,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" s="19">
         <f t="shared" si="2"/>
         <v>80</v>
@@ -4014,7 +4025,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" s="19">
         <f t="shared" si="2"/>
         <v>81</v>
@@ -4035,7 +4046,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" s="19">
         <f t="shared" si="2"/>
         <v>82</v>
@@ -4056,7 +4067,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="19">
         <f t="shared" si="2"/>
         <v>83</v>
@@ -4077,7 +4088,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" s="19">
         <f t="shared" si="2"/>
         <v>84</v>
@@ -4098,7 +4109,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" s="19">
         <v>80</v>
       </c>
@@ -4118,7 +4129,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" s="19">
         <f t="shared" si="2"/>
         <v>81</v>
@@ -4139,7 +4150,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="19">
         <f t="shared" si="2"/>
         <v>82</v>
@@ -4160,7 +4171,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" s="19">
         <f t="shared" si="2"/>
         <v>83</v>
@@ -4181,7 +4192,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="19">
         <f t="shared" si="2"/>
         <v>84</v>
@@ -4202,7 +4213,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" s="19">
         <f t="shared" si="2"/>
         <v>85</v>
@@ -4223,7 +4234,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" s="19">
         <v>81</v>
       </c>
@@ -4243,7 +4254,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" s="19">
         <f t="shared" si="2"/>
         <v>82</v>
@@ -4264,7 +4275,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" s="19">
         <f t="shared" si="2"/>
         <v>83</v>
@@ -4285,7 +4296,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" s="19">
         <f t="shared" si="2"/>
         <v>84</v>
@@ -4306,7 +4317,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" s="19">
         <f t="shared" si="2"/>
         <v>85</v>
@@ -4327,7 +4338,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" s="19">
         <f t="shared" si="2"/>
         <v>86</v>
@@ -4348,7 +4359,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="19">
         <v>82</v>
       </c>
@@ -4368,7 +4379,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" s="19">
         <f t="shared" si="2"/>
         <v>83</v>
@@ -4389,7 +4400,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="19">
         <f t="shared" si="2"/>
         <v>84</v>
@@ -4410,7 +4421,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" s="19">
         <f t="shared" si="2"/>
         <v>85</v>
@@ -4431,7 +4442,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" s="19">
         <f t="shared" si="2"/>
         <v>86</v>
@@ -4452,7 +4463,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" s="19">
         <f t="shared" si="2"/>
         <v>87</v>
@@ -4473,7 +4484,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" s="19">
         <v>83</v>
       </c>
@@ -4493,7 +4504,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" s="19">
         <f t="shared" si="2"/>
         <v>84</v>
@@ -4514,7 +4525,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="19">
         <f t="shared" si="2"/>
         <v>85</v>
@@ -4535,7 +4546,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" s="19">
         <f t="shared" si="2"/>
         <v>86</v>
@@ -4556,7 +4567,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" s="19">
         <f t="shared" si="2"/>
         <v>87</v>
@@ -4577,7 +4588,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" s="19">
         <f t="shared" si="2"/>
         <v>88</v>
@@ -4598,7 +4609,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="19">
         <v>84</v>
       </c>
@@ -4618,7 +4629,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" s="19">
         <f t="shared" si="2"/>
         <v>85</v>
@@ -4639,7 +4650,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" s="19">
         <f t="shared" si="2"/>
         <v>86</v>
@@ -4660,7 +4671,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" s="19">
         <f t="shared" si="2"/>
         <v>87</v>
@@ -4681,7 +4692,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" s="19">
         <v>88</v>
       </c>
@@ -4701,7 +4712,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" s="19">
         <f t="shared" si="2"/>
         <v>89</v>
@@ -4722,7 +4733,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" s="19">
         <v>90</v>
       </c>
@@ -4742,7 +4753,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" s="19">
         <f t="shared" si="2"/>
         <v>91</v>
@@ -4763,7 +4774,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" s="19">
         <v>92</v>
       </c>
@@ -4783,7 +4794,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" s="19">
         <v>93</v>
       </c>
@@ -4803,7 +4814,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" s="19">
         <v>94</v>
       </c>
@@ -4823,7 +4834,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" s="19">
         <v>95</v>
       </c>
@@ -4843,7 +4854,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" s="19">
         <v>96</v>
       </c>
@@ -4863,7 +4874,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125" s="19">
         <v>97</v>
       </c>
@@ -4883,7 +4894,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" s="19">
         <v>98</v>
       </c>
@@ -4915,24 +4926,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{620FB88A-C9C3-47FD-BB4D-39DF868892A8}">
-  <dimension ref="A1:F126"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>158</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>338</v>
-      </c>
-    </row>
-    <row r="126" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F126" t="s">
-        <v>372</v>
       </c>
     </row>
   </sheetData>
